--- a/spider_telephone/电话号码判断6.xlsx
+++ b/spider_telephone/电话号码判断6.xlsx
@@ -432,481 +432,641 @@
       <c r="A2" t="n">
         <v>13790393954</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>13790405589</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>13790419056</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>13790421095</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>13790458353</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>13790483302</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>13790494488</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>13790494902</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>13790578973</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>13790601572</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>13790683138</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>13790687776</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13790689947</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13790691705</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13794868255</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13794949764</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13798781472</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13798781690</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13798823821</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13798843237</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13798855625</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13798856719</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13798881331</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13798895886</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13798896320</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13798898561</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13798930665</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13798933533</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13802386445</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13802397109</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13809616372</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13809619132</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13809644011</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13809827203</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13825720922</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13825730587</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13825764627</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13825778943</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13825780799</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13826944862</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13826958639</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13826985060</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13827230263</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13827244150</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13827244258</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13827244347</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13827247099</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13827279440</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13827299884</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13829118773</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13829134489</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13829159456</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13829220547</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13829225427</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13829233780</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13829250308</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13829252724</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13829253711</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13829269116</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13829283209</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13902605162</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13902615601</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13902646515</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13903034038</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13922535233</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13922909248</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13922920808</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13922954099</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13922963288</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13922969663</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13924338129</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13924338938</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13924352371</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13924364713</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13925503695</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13925513168</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13925560363</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13925569861</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13925583326</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13925705688</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spider_telephone/电话号码判断6.xlsx
+++ b/spider_telephone/电话号码判断6.xlsx
@@ -528,544 +528,680 @@
       <c r="A14" t="n">
         <v>13790689947</v>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13790691705</v>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13794868255</v>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13794949764</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13798781472</v>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13798781690</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13798823821</v>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13798843237</v>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13798855625</v>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13798856719</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13798881331</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13798895886</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13798896320</v>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13798898561</v>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13798930665</v>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13798933533</v>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13802386445</v>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13802397109</v>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13809616372</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13809619132</v>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13809644011</v>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13809827203</v>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13825720922</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13825730587</v>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13825764627</v>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13825778943</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13825780799</v>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13826944862</v>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13826958639</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13826985060</v>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13827230263</v>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13827244150</v>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13827244258</v>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13827244347</v>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13827247099</v>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13827279440</v>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13827299884</v>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13829118773</v>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13829134489</v>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13829159456</v>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13829220547</v>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13829225427</v>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13829233780</v>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13829250308</v>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13829252724</v>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13829253711</v>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13829269116</v>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13829283209</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13902605162</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13902615601</v>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13902646515</v>
       </c>
-      <c r="B64" t="n">
-        <v>1</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13903034038</v>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13922535233</v>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13922909248</v>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13922920808</v>
       </c>
-      <c r="B68" t="n">
-        <v>1</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13922954099</v>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13922963288</v>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13922969663</v>
       </c>
-      <c r="B71" t="n">
-        <v>1</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13924338129</v>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13924338938</v>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13924352371</v>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13924364713</v>
       </c>
-      <c r="B75" t="n">
-        <v>1</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13925503695</v>
       </c>
-      <c r="B76" t="n">
-        <v>1</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13925513168</v>
       </c>
-      <c r="B77" t="n">
-        <v>1</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13925560363</v>
       </c>
-      <c r="B78" t="n">
-        <v>1</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13925569861</v>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13925583326</v>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13925705688</v>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
   </sheetData>
